--- a/tests/testthat/fixtures/acirl/2400-9999-13_AlsRefs_WMF.xlsx
+++ b/tests/testthat/fixtures/acirl/2400-9999-13_AlsRefs_WMF.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">ALS COAL DIVISION</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t xml:space="preserve">Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALS Lithogw Report No</t>
   </si>
   <si>
     <t xml:space="preserve">ALS Sydney Report No.</t>
@@ -549,16 +552,22 @@
       </c>
     </row>
     <row r="6">
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -571,7 +580,7 @@
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>45801</v>
@@ -588,61 +597,61 @@
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
         <v>22</v>
-      </c>
-      <c r="G12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
         <v>21</v>
@@ -659,10 +668,10 @@
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
         <v>5.9</v>
@@ -679,10 +688,10 @@
     </row>
     <row r="15">
       <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
         <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
       </c>
       <c r="D15" t="n">
         <v>6.42</v>
@@ -699,10 +708,10 @@
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>1265</v>
@@ -719,10 +728,10 @@
     </row>
     <row r="17">
       <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
         <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>1360</v>
@@ -739,30 +748,30 @@
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" t="n">
         <v>5.41</v>
@@ -776,32 +785,32 @@
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" t="s">
         <v>40</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" t="n">
         <v>0.4</v>
@@ -818,10 +827,10 @@
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" t="n">
         <v>24</v>
@@ -838,10 +847,10 @@
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24" t="n">
         <v>310</v>
@@ -858,10 +867,10 @@
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D25" t="n">
         <v>140</v>
@@ -909,10 +918,10 @@
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -925,7 +934,7 @@
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>45801</v>
@@ -942,61 +951,61 @@
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
         <v>22</v>
-      </c>
-      <c r="G12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
         <v>21</v>
@@ -1013,10 +1022,10 @@
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
         <v>5.9</v>
@@ -1033,10 +1042,10 @@
     </row>
     <row r="15">
       <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
         <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
       </c>
       <c r="D15" t="n">
         <v>6.42</v>
@@ -1053,10 +1062,10 @@
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>1265</v>
@@ -1073,10 +1082,10 @@
     </row>
     <row r="17">
       <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
         <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>1360</v>
@@ -1093,30 +1102,30 @@
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" t="n">
         <v>5.41</v>
@@ -1130,32 +1139,32 @@
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" t="s">
         <v>40</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" t="n">
         <v>0.4</v>
@@ -1172,10 +1181,10 @@
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" t="n">
         <v>24</v>
@@ -1192,10 +1201,10 @@
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24" t="n">
         <v>310</v>
@@ -1212,10 +1221,10 @@
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D25" t="n">
         <v>140</v>
@@ -1263,7 +1272,7 @@
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
@@ -1279,7 +1288,7 @@
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>45801</v>
@@ -1296,61 +1305,61 @@
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
         <v>22</v>
-      </c>
-      <c r="G12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
         <v>21</v>
@@ -1367,10 +1376,10 @@
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
         <v>5.9</v>
@@ -1387,10 +1396,10 @@
     </row>
     <row r="15">
       <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
         <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
       </c>
       <c r="D15" t="n">
         <v>6.42</v>
@@ -1407,10 +1416,10 @@
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>1265</v>
@@ -1427,10 +1436,10 @@
     </row>
     <row r="17">
       <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
         <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>1360</v>
@@ -1447,30 +1456,30 @@
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" t="n">
         <v>5.41</v>
@@ -1484,32 +1493,32 @@
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" t="s">
         <v>40</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" t="n">
         <v>0.4</v>
@@ -1526,10 +1535,10 @@
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" t="n">
         <v>24</v>
@@ -1546,10 +1555,10 @@
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24" t="n">
         <v>310</v>
@@ -1566,10 +1575,10 @@
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D25" t="n">
         <v>140</v>
@@ -1617,7 +1626,7 @@
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1630,7 +1639,7 @@
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>45801</v>
@@ -1647,61 +1656,61 @@
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
         <v>22</v>
-      </c>
-      <c r="G12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
         <v>21</v>
@@ -1718,10 +1727,10 @@
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
         <v>5.9</v>
@@ -1738,10 +1747,10 @@
     </row>
     <row r="15">
       <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
         <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
       </c>
       <c r="D15" t="n">
         <v>6.42</v>
@@ -1758,10 +1767,10 @@
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>1265</v>
@@ -1778,10 +1787,10 @@
     </row>
     <row r="17">
       <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
         <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>1360</v>
@@ -1798,30 +1807,30 @@
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" t="n">
         <v>5.41</v>
@@ -1835,32 +1844,32 @@
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" t="s">
         <v>40</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" t="n">
         <v>0.4</v>
@@ -1877,10 +1886,10 @@
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" t="n">
         <v>24</v>
@@ -1897,10 +1906,10 @@
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24" t="n">
         <v>310</v>
@@ -1917,10 +1926,10 @@
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D25" t="n">
         <v>140</v>
